--- a/314e-ig/output/StructureDefinition-datarequirement-314e.xlsx
+++ b/314e-ig/output/StructureDefinition-datarequirement-314e.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-11T14:17:09+05:30</t>
+    <t>2026-06-18T13:36:33+05:30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/314e-ig/output/StructureDefinition-datarequirement-314e.xlsx
+++ b/314e-ig/output/StructureDefinition-datarequirement-314e.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-18T13:36:33+05:30</t>
+    <t>2026-06-18T14:15:04+05:30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/314e-ig/output/StructureDefinition-datarequirement-314e.xlsx
+++ b/314e-ig/output/StructureDefinition-datarequirement-314e.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-18T14:15:04+05:30</t>
+    <t>2026-06-18T16:14:31+05:30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/314e-ig/output/StructureDefinition-datarequirement-314e.xlsx
+++ b/314e-ig/output/StructureDefinition-datarequirement-314e.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-18T16:14:31+05:30</t>
+    <t>2026-06-24T16:34:23+05:30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/314e-ig/output/StructureDefinition-datarequirement-314e.xlsx
+++ b/314e-ig/output/StructureDefinition-datarequirement-314e.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="918" uniqueCount="182">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="952" uniqueCount="186">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-24T16:34:23+05:30</t>
+    <t>2026-06-29T17:18:47+05:30</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -364,7 +364,7 @@
   </si>
   <si>
     <t>CodeableConcept {http://314e.com/fhir/ig/StructureDefinition/codeableconcept-314e}
-Reference(Group) {http://314e.com/fhir/StructureDefinition/reference-314e}</t>
+Reference(http://314e.com/fhir/StructureDefinition/group-314e) {http://314e.com/fhir/StructureDefinition/reference-314e}</t>
   </si>
   <si>
     <t>E.g. Patient, Practitioner, RelatedPerson, Organization, Location, Device</t>
@@ -386,6 +386,20 @@
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/subject-type|4.0.1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">type:$this}
+</t>
+  </si>
+  <si>
+    <t>DataRequirement.subject[x]:subjectReference</t>
+  </si>
+  <si>
+    <t>subjectReference</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference(http://314e.com/fhir/StructureDefinition/group-314e) {http://314e.com/fhir/StructureDefinition/reference-314e}
+</t>
   </si>
   <si>
     <t>DataRequirement.mustSupport</t>
@@ -881,12 +895,12 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AK27"/>
+  <dimension ref="A1:AK28"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="34.66015625" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="38.03515625" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="34.66015625" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="9.984375" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="3" max="3" width="14.8828125" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="11.10546875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="5.29296875" customWidth="true" bestFit="true"/>
     <col min="6" max="6" width="4.21484375" customWidth="true" bestFit="true"/>
@@ -1629,16 +1643,14 @@
         <v>20</v>
       </c>
       <c r="AB7" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AC7" t="s" s="2">
-        <v>20</v>
-      </c>
+        <v>120</v>
+      </c>
+      <c r="AC7" s="2"/>
       <c r="AD7" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AE7" t="s" s="2">
-        <v>20</v>
+        <v>96</v>
       </c>
       <c r="AF7" t="s" s="2">
         <v>111</v>
@@ -1661,12 +1673,14 @@
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>120</v>
-      </c>
-      <c r="C8" s="2"/>
+        <v>111</v>
+      </c>
+      <c r="C8" t="s" s="2">
+        <v>122</v>
+      </c>
       <c r="D8" t="s" s="2">
         <v>20</v>
       </c>
@@ -1675,7 +1689,7 @@
         <v>74</v>
       </c>
       <c r="G8" t="s" s="2">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="H8" t="s" s="2">
         <v>20</v>
@@ -1687,20 +1701,24 @@
         <v>100</v>
       </c>
       <c r="K8" t="s" s="2">
-        <v>84</v>
+        <v>123</v>
       </c>
       <c r="L8" t="s" s="2">
-        <v>121</v>
+        <v>113</v>
       </c>
       <c r="M8" t="s" s="2">
-        <v>122</v>
-      </c>
-      <c r="N8" s="2"/>
+        <v>114</v>
+      </c>
+      <c r="N8" t="s" s="2">
+        <v>115</v>
+      </c>
       <c r="O8" s="2"/>
       <c r="P8" t="s" s="2">
         <v>20</v>
       </c>
-      <c r="Q8" s="2"/>
+      <c r="Q8" t="s" s="2">
+        <v>116</v>
+      </c>
       <c r="R8" t="s" s="2">
         <v>20</v>
       </c>
@@ -1744,13 +1762,13 @@
         <v>20</v>
       </c>
       <c r="AF8" t="s" s="2">
-        <v>120</v>
+        <v>111</v>
       </c>
       <c r="AG8" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH8" t="s" s="2">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="AI8" t="s" s="2">
         <v>20</v>
@@ -1764,10 +1782,10 @@
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
@@ -1790,7 +1808,7 @@
         <v>100</v>
       </c>
       <c r="K9" t="s" s="2">
-        <v>124</v>
+        <v>84</v>
       </c>
       <c r="L9" t="s" s="2">
         <v>125</v>
@@ -1847,7 +1865,7 @@
         <v>20</v>
       </c>
       <c r="AF9" t="s" s="2">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="AG9" t="s" s="2">
         <v>74</v>
@@ -1859,7 +1877,7 @@
         <v>20</v>
       </c>
       <c r="AJ9" t="s" s="2">
-        <v>127</v>
+        <v>80</v>
       </c>
       <c r="AK9" t="s" s="2">
         <v>20</v>
@@ -1867,10 +1885,10 @@
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C10" s="2"/>
       <c r="D10" t="s" s="2">
@@ -1881,7 +1899,7 @@
         <v>74</v>
       </c>
       <c r="G10" t="s" s="2">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="H10" t="s" s="2">
         <v>20</v>
@@ -1890,16 +1908,16 @@
         <v>20</v>
       </c>
       <c r="J10" t="s" s="2">
-        <v>20</v>
+        <v>100</v>
       </c>
       <c r="K10" t="s" s="2">
-        <v>84</v>
+        <v>128</v>
       </c>
       <c r="L10" t="s" s="2">
-        <v>85</v>
+        <v>129</v>
       </c>
       <c r="M10" t="s" s="2">
-        <v>86</v>
+        <v>130</v>
       </c>
       <c r="N10" s="2"/>
       <c r="O10" s="2"/>
@@ -1950,41 +1968,41 @@
         <v>20</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>87</v>
+        <v>127</v>
       </c>
       <c r="AG10" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH10" t="s" s="2">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="AI10" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ10" t="s" s="2">
-        <v>20</v>
+        <v>131</v>
       </c>
       <c r="AK10" t="s" s="2">
-        <v>81</v>
+        <v>20</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
-        <v>89</v>
+        <v>20</v>
       </c>
       <c r="E11" s="2"/>
       <c r="F11" t="s" s="2">
         <v>74</v>
       </c>
       <c r="G11" t="s" s="2">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="H11" t="s" s="2">
         <v>20</v>
@@ -1996,17 +2014,15 @@
         <v>20</v>
       </c>
       <c r="K11" t="s" s="2">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="L11" t="s" s="2">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="M11" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="N11" t="s" s="2">
-        <v>93</v>
-      </c>
+        <v>86</v>
+      </c>
+      <c r="N11" s="2"/>
       <c r="O11" s="2"/>
       <c r="P11" t="s" s="2">
         <v>20</v>
@@ -2043,31 +2059,31 @@
         <v>20</v>
       </c>
       <c r="AB11" t="s" s="2">
-        <v>94</v>
+        <v>20</v>
       </c>
       <c r="AC11" t="s" s="2">
-        <v>95</v>
+        <v>20</v>
       </c>
       <c r="AD11" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AE11" t="s" s="2">
-        <v>96</v>
+        <v>20</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>97</v>
+        <v>87</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH11" t="s" s="2">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="AI11" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ11" t="s" s="2">
-        <v>98</v>
+        <v>20</v>
       </c>
       <c r="AK11" t="s" s="2">
         <v>81</v>
@@ -2075,21 +2091,21 @@
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
-        <v>20</v>
+        <v>89</v>
       </c>
       <c r="E12" s="2"/>
       <c r="F12" t="s" s="2">
         <v>74</v>
       </c>
       <c r="G12" t="s" s="2">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="H12" t="s" s="2">
         <v>20</v>
@@ -2098,19 +2114,19 @@
         <v>20</v>
       </c>
       <c r="J12" t="s" s="2">
-        <v>100</v>
+        <v>20</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>131</v>
+        <v>91</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>132</v>
+        <v>92</v>
       </c>
       <c r="N12" t="s" s="2">
-        <v>133</v>
+        <v>93</v>
       </c>
       <c r="O12" s="2"/>
       <c r="P12" t="s" s="2">
@@ -2148,34 +2164,34 @@
         <v>20</v>
       </c>
       <c r="AB12" t="s" s="2">
-        <v>20</v>
+        <v>94</v>
       </c>
       <c r="AC12" t="s" s="2">
-        <v>20</v>
+        <v>95</v>
       </c>
       <c r="AD12" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AE12" t="s" s="2">
-        <v>20</v>
+        <v>96</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>130</v>
+        <v>97</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH12" t="s" s="2">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="AI12" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ12" t="s" s="2">
-        <v>80</v>
+        <v>98</v>
       </c>
       <c r="AK12" t="s" s="2">
-        <v>20</v>
+        <v>81</v>
       </c>
     </row>
     <row r="13">
@@ -2214,7 +2230,9 @@
       <c r="M13" t="s" s="2">
         <v>136</v>
       </c>
-      <c r="N13" s="2"/>
+      <c r="N13" t="s" s="2">
+        <v>137</v>
+      </c>
       <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
         <v>20</v>
@@ -2283,10 +2301,10 @@
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -2309,7 +2327,7 @@
         <v>100</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>138</v>
+        <v>84</v>
       </c>
       <c r="L14" t="s" s="2">
         <v>139</v>
@@ -2366,7 +2384,7 @@
         <v>20</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>74</v>
@@ -2400,7 +2418,7 @@
         <v>74</v>
       </c>
       <c r="G15" t="s" s="2">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="H15" t="s" s="2">
         <v>20</v>
@@ -2475,7 +2493,7 @@
         <v>74</v>
       </c>
       <c r="AH15" t="s" s="2">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="AI15" t="s" s="2">
         <v>20</v>
@@ -2515,13 +2533,13 @@
         <v>100</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>124</v>
+        <v>146</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="N16" s="2"/>
       <c r="O16" s="2"/>
@@ -2584,7 +2602,7 @@
         <v>20</v>
       </c>
       <c r="AJ16" t="s" s="2">
-        <v>148</v>
+        <v>80</v>
       </c>
       <c r="AK16" t="s" s="2">
         <v>20</v>
@@ -2606,7 +2624,7 @@
         <v>74</v>
       </c>
       <c r="G17" t="s" s="2">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="H17" t="s" s="2">
         <v>20</v>
@@ -2615,16 +2633,16 @@
         <v>20</v>
       </c>
       <c r="J17" t="s" s="2">
-        <v>20</v>
+        <v>100</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>84</v>
+        <v>128</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>85</v>
+        <v>150</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>86</v>
+        <v>151</v>
       </c>
       <c r="N17" s="2"/>
       <c r="O17" s="2"/>
@@ -2675,41 +2693,41 @@
         <v>20</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>87</v>
+        <v>149</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH17" t="s" s="2">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="AI17" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ17" t="s" s="2">
-        <v>20</v>
+        <v>152</v>
       </c>
       <c r="AK17" t="s" s="2">
-        <v>81</v>
+        <v>20</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
-        <v>89</v>
+        <v>20</v>
       </c>
       <c r="E18" s="2"/>
       <c r="F18" t="s" s="2">
         <v>74</v>
       </c>
       <c r="G18" t="s" s="2">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="H18" t="s" s="2">
         <v>20</v>
@@ -2721,17 +2739,15 @@
         <v>20</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="N18" t="s" s="2">
-        <v>93</v>
-      </c>
+        <v>86</v>
+      </c>
+      <c r="N18" s="2"/>
       <c r="O18" s="2"/>
       <c r="P18" t="s" s="2">
         <v>20</v>
@@ -2768,31 +2784,31 @@
         <v>20</v>
       </c>
       <c r="AB18" t="s" s="2">
-        <v>94</v>
+        <v>20</v>
       </c>
       <c r="AC18" t="s" s="2">
-        <v>95</v>
+        <v>20</v>
       </c>
       <c r="AD18" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AE18" t="s" s="2">
-        <v>96</v>
+        <v>20</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>97</v>
+        <v>87</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH18" t="s" s="2">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="AI18" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ18" t="s" s="2">
-        <v>98</v>
+        <v>20</v>
       </c>
       <c r="AK18" t="s" s="2">
         <v>81</v>
@@ -2800,21 +2816,21 @@
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
-        <v>20</v>
+        <v>89</v>
       </c>
       <c r="E19" s="2"/>
       <c r="F19" t="s" s="2">
         <v>74</v>
       </c>
       <c r="G19" t="s" s="2">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="H19" t="s" s="2">
         <v>20</v>
@@ -2823,19 +2839,19 @@
         <v>20</v>
       </c>
       <c r="J19" t="s" s="2">
-        <v>100</v>
+        <v>20</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>152</v>
+        <v>91</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>153</v>
+        <v>92</v>
       </c>
       <c r="N19" t="s" s="2">
-        <v>154</v>
+        <v>93</v>
       </c>
       <c r="O19" s="2"/>
       <c r="P19" t="s" s="2">
@@ -2873,34 +2889,34 @@
         <v>20</v>
       </c>
       <c r="AB19" t="s" s="2">
-        <v>20</v>
+        <v>94</v>
       </c>
       <c r="AC19" t="s" s="2">
-        <v>20</v>
+        <v>95</v>
       </c>
       <c r="AD19" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AE19" t="s" s="2">
-        <v>20</v>
+        <v>96</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>151</v>
+        <v>97</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH19" t="s" s="2">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="AI19" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ19" t="s" s="2">
-        <v>80</v>
+        <v>98</v>
       </c>
       <c r="AK19" t="s" s="2">
-        <v>20</v>
+        <v>81</v>
       </c>
     </row>
     <row r="20">
@@ -2939,7 +2955,9 @@
       <c r="M20" t="s" s="2">
         <v>157</v>
       </c>
-      <c r="N20" s="2"/>
+      <c r="N20" t="s" s="2">
+        <v>158</v>
+      </c>
       <c r="O20" s="2"/>
       <c r="P20" t="s" s="2">
         <v>20</v>
@@ -3008,10 +3026,10 @@
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -3034,7 +3052,7 @@
         <v>100</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>159</v>
+        <v>84</v>
       </c>
       <c r="L21" t="s" s="2">
         <v>160</v>
@@ -3091,7 +3109,7 @@
         <v>20</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>74</v>
@@ -3145,12 +3163,8 @@
       <c r="M22" t="s" s="2">
         <v>165</v>
       </c>
-      <c r="N22" t="s" s="2">
-        <v>166</v>
-      </c>
-      <c r="O22" t="s" s="2">
-        <v>167</v>
-      </c>
+      <c r="N22" s="2"/>
+      <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
         <v>20</v>
       </c>
@@ -3218,10 +3232,10 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -3232,7 +3246,7 @@
         <v>74</v>
       </c>
       <c r="G23" t="s" s="2">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="H23" t="s" s="2">
         <v>20</v>
@@ -3244,19 +3258,19 @@
         <v>100</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>124</v>
+        <v>167</v>
       </c>
       <c r="L23" t="s" s="2">
+        <v>168</v>
+      </c>
+      <c r="M23" t="s" s="2">
         <v>169</v>
       </c>
-      <c r="M23" t="s" s="2">
+      <c r="N23" t="s" s="2">
         <v>170</v>
       </c>
-      <c r="N23" t="s" s="2">
+      <c r="O23" t="s" s="2">
         <v>171</v>
-      </c>
-      <c r="O23" t="s" s="2">
-        <v>167</v>
       </c>
       <c r="P23" t="s" s="2">
         <v>20</v>
@@ -3305,13 +3319,13 @@
         <v>20</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH23" t="s" s="2">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="AI23" t="s" s="2">
         <v>20</v>
@@ -3339,7 +3353,7 @@
         <v>74</v>
       </c>
       <c r="G24" t="s" s="2">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="H24" t="s" s="2">
         <v>20</v>
@@ -3348,19 +3362,23 @@
         <v>20</v>
       </c>
       <c r="J24" t="s" s="2">
-        <v>20</v>
+        <v>100</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>84</v>
+        <v>128</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>85</v>
+        <v>173</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>86</v>
-      </c>
-      <c r="N24" s="2"/>
-      <c r="O24" s="2"/>
+        <v>174</v>
+      </c>
+      <c r="N24" t="s" s="2">
+        <v>175</v>
+      </c>
+      <c r="O24" t="s" s="2">
+        <v>171</v>
+      </c>
       <c r="P24" t="s" s="2">
         <v>20</v>
       </c>
@@ -3408,41 +3426,41 @@
         <v>20</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>87</v>
+        <v>172</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH24" t="s" s="2">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="AI24" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ24" t="s" s="2">
-        <v>20</v>
+        <v>80</v>
       </c>
       <c r="AK24" t="s" s="2">
-        <v>81</v>
+        <v>20</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
-        <v>89</v>
+        <v>20</v>
       </c>
       <c r="E25" s="2"/>
       <c r="F25" t="s" s="2">
         <v>74</v>
       </c>
       <c r="G25" t="s" s="2">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="H25" t="s" s="2">
         <v>20</v>
@@ -3454,17 +3472,15 @@
         <v>20</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="N25" t="s" s="2">
-        <v>93</v>
-      </c>
+        <v>86</v>
+      </c>
+      <c r="N25" s="2"/>
       <c r="O25" s="2"/>
       <c r="P25" t="s" s="2">
         <v>20</v>
@@ -3501,31 +3517,31 @@
         <v>20</v>
       </c>
       <c r="AB25" t="s" s="2">
-        <v>94</v>
+        <v>20</v>
       </c>
       <c r="AC25" t="s" s="2">
-        <v>95</v>
+        <v>20</v>
       </c>
       <c r="AD25" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AE25" t="s" s="2">
-        <v>96</v>
+        <v>20</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>97</v>
+        <v>87</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH25" t="s" s="2">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="AI25" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ25" t="s" s="2">
-        <v>98</v>
+        <v>20</v>
       </c>
       <c r="AK25" t="s" s="2">
         <v>81</v>
@@ -3533,21 +3549,21 @@
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
-        <v>20</v>
+        <v>89</v>
       </c>
       <c r="E26" s="2"/>
       <c r="F26" t="s" s="2">
-        <v>83</v>
+        <v>74</v>
       </c>
       <c r="G26" t="s" s="2">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="H26" t="s" s="2">
         <v>20</v>
@@ -3556,18 +3572,20 @@
         <v>20</v>
       </c>
       <c r="J26" t="s" s="2">
-        <v>100</v>
+        <v>20</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>175</v>
+        <v>91</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>176</v>
-      </c>
-      <c r="N26" s="2"/>
+        <v>92</v>
+      </c>
+      <c r="N26" t="s" s="2">
+        <v>93</v>
+      </c>
       <c r="O26" s="2"/>
       <c r="P26" t="s" s="2">
         <v>20</v>
@@ -3604,42 +3622,42 @@
         <v>20</v>
       </c>
       <c r="AB26" t="s" s="2">
-        <v>20</v>
+        <v>94</v>
       </c>
       <c r="AC26" t="s" s="2">
-        <v>20</v>
+        <v>95</v>
       </c>
       <c r="AD26" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AE26" t="s" s="2">
-        <v>20</v>
+        <v>96</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>174</v>
+        <v>97</v>
       </c>
       <c r="AG26" t="s" s="2">
-        <v>83</v>
+        <v>74</v>
       </c>
       <c r="AH26" t="s" s="2">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="AI26" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ26" t="s" s="2">
-        <v>80</v>
+        <v>98</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>20</v>
+        <v>81</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -3662,13 +3680,13 @@
         <v>100</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>101</v>
+        <v>84</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="N27" s="2"/>
       <c r="O27" s="2"/>
@@ -3695,13 +3713,13 @@
         <v>20</v>
       </c>
       <c r="X27" t="s" s="2">
-        <v>104</v>
+        <v>20</v>
       </c>
       <c r="Y27" t="s" s="2">
-        <v>180</v>
+        <v>20</v>
       </c>
       <c r="Z27" t="s" s="2">
-        <v>181</v>
+        <v>20</v>
       </c>
       <c r="AA27" t="s" s="2">
         <v>20</v>
@@ -3719,7 +3737,7 @@
         <v>20</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>83</v>
@@ -3734,6 +3752,109 @@
         <v>80</v>
       </c>
       <c r="AK27" t="s" s="2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="s" s="2">
+        <v>181</v>
+      </c>
+      <c r="B28" t="s" s="2">
+        <v>181</v>
+      </c>
+      <c r="C28" s="2"/>
+      <c r="D28" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="E28" s="2"/>
+      <c r="F28" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="G28" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="H28" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="I28" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="J28" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="K28" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="L28" t="s" s="2">
+        <v>182</v>
+      </c>
+      <c r="M28" t="s" s="2">
+        <v>183</v>
+      </c>
+      <c r="N28" s="2"/>
+      <c r="O28" s="2"/>
+      <c r="P28" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Q28" s="2"/>
+      <c r="R28" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="S28" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="T28" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="U28" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V28" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W28" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X28" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="Y28" t="s" s="2">
+        <v>184</v>
+      </c>
+      <c r="Z28" t="s" s="2">
+        <v>185</v>
+      </c>
+      <c r="AA28" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB28" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC28" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD28" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE28" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF28" t="s" s="2">
+        <v>181</v>
+      </c>
+      <c r="AG28" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AH28" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AI28" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AJ28" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AK28" t="s" s="2">
         <v>20</v>
       </c>
     </row>

--- a/314e-ig/output/StructureDefinition-datarequirement-314e.xlsx
+++ b/314e-ig/output/StructureDefinition-datarequirement-314e.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-29T17:18:47+05:30</t>
+    <t>2026-07-01T18:18:44+05:30</t>
   </si>
   <si>
     <t>Publisher</t>
